--- a/_tmp_archive/v49_build_workdir_cleanup/CKI_Supplementary_Tables_NC.xlsx
+++ b/_tmp_archive/v49_build_workdir_cleanup/CKI_Supplementary_Tables_NC.xlsx
@@ -440,7 +440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 5: Linear-normalization robustness of the TCGA main pipeline. Every qualitative conclusion is preserved: the tumor-normal versus baseline contrast stays significant in all five cancer types (all TN/baseline ω &lt; 1; permutation P = 1 × 10⁻⁴⁹ to 1 × 10⁻¹⁴), with ratios attenuating slightly toward 1; the NN &gt; TT ω reversal is retained in 5 of 5 cancer types with the k_n reversal (TT k_n 2.1–3.6× the NN median) intact; k_n &lt; 1 × 10⁻⁴ floor saturation is &lt; 0.1% under the linear mapping (a single pair of 35,306 at k_n = 8.4 × 10⁻⁵; all other pair-level k_n ≈ 7 × 10⁻⁴ to 6 × 10⁻³), so the floor is not an artifact of the mapping; all three clinical-severity orderings are preserved (full values in Supplementary Note 9); and the composition-sensitivity conclusion is unchanged (pooled tumor-pair coefficient attenuation −0.8%, cluster-bootstrap median −1.2% [95% CI −4.1%, +2.6%]; Supplementary Note 8). One quantitative caveat: the LIHC NN/TT effect size is mapping-sensitive - the mean NN/TT ω ratio is 1.10 under the linear mapping versus 1.31 under the softmax mapping - so the LIHC reversal, though directionally preserved, is quantitatively weaker in the authoritative linear caliber.</t>
+          <t>Supplementary Table 5: Two-caliber NN/TT ω reversal table (ex-CC cohort, v52). Mean NN/TT ω ratio with sample-level cluster-bootstrap 95% CI (B = 1,000, seed 42) under the authoritative linear probability mapping and the legacy softmax mapping. The reversal direction is preserved in 5 of 5 cancer types under both calibers; the count of CIs excluding 1 is mapping-sensitive only through LIHC (four of five linear, five of five softmax), so the main-text "four of five" statement is conservative. Floor sensitivity: k_n floor settings 0, 1 × 10⁻⁵, and 1 × 10⁻⁴ leave every ratio identical (no pair-level k_n falls in (0, 10⁻⁴); results/nc52_tcga_knfloor_sensitivity.csv), while 1 × 10⁻³ truncates ~50% of NN pairs and attenuates the reversal (LUAD 2.464 → 1.494; BRCA below 1), quantifying the floor dependence; all three clinical-severity orderings are preserved (full values in Supplementary Note 9), and the composition-sensitivity conclusion is unchanged (pooled tumor-pair coefficient attenuation −1.3%, cluster-bootstrap median −1.3% [95% CI −4.8%, +2.0%] at B = 1,000; Supplementary Note 8).</t>
         </is>
       </c>
     </row>
@@ -452,22 +452,22 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>TN/baseline ω (softmax)</t>
+          <t>NN/TT ω (linear) [95% CI]</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>TN/baseline ω (linear)</t>
+          <t>CI excl. 1</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>NN &gt; TT ω reversal</t>
+          <t>NN/TT ω (softmax) [95% CI]</t>
         </is>
       </c>
       <c r="E3" s="1" t="inlineStr">
         <is>
-          <t>TT/NN k_n fold (linear)</t>
+          <t>CI excl. 1</t>
         </is>
       </c>
     </row>
@@ -479,22 +479,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>2.464 [2.128, 2.863]</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>retained</t>
+          <t>2.620 [2.265, 3.042]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.6×</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -506,22 +506,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.708 [1.378, 2.087]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>retained</t>
+          <t>1.885 [1.508, 2.294]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.7×</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -533,22 +533,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.112 [0.943, 1.302]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>retained</t>
+          <t>1.286 [1.091, 1.533]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2.1×</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -560,22 +560,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.880 [1.638, 2.148]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>retained</t>
+          <t>2.046 [1.760, 2.335]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.6×</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -587,22 +587,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.567 [1.342, 1.815]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>retained</t>
+          <t>1.748 [1.511, 2.009]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2.8×</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Supplementary Table 14: LIHC overall-survival Cox models (hazard ratios per +1 SD of the exposure). No exposure reaches significance (all P ≥ 0.07; k_f closest at P = 0.072), so the pan-cancer reversal is a descriptive property of tissue-state divergence, not a prognostic marker; the full coefficient table is results/nc49_pilot_lihc_cox.csv of the companion repository.</t>
+          <t>Supplementary Table 14: LIHC overall-survival Cox models (hazard ratios per +1 SD of the exposure; ex-CC cohort, n = 272 with 79 events; R survival::coxph with AJCC stage as a categorical covariate; proportional-hazards checked by cox.zph—M2 shows a GLOBAL departure signal at P = 0.023, all other models P ≥ 0.07). No exposure reaches significance (all P ≥ 0.39), so the pan-cancer reversal is a descriptive property of tissue-state divergence, not a prognostic marker; the full coefficient table is results/nc52_lihc_cox_excc.csv of the companion repository.</t>
         </is>
       </c>
     </row>
@@ -665,22 +665,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.07 [0.88, 1.31]</t>
+          <t>1.08 [0.88, 1.33]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.47</t>
         </is>
       </c>
     </row>
@@ -692,22 +692,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.04 [0.86, 1.27]</t>
+          <t>1.00 [0.82, 1.22]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.99</t>
         </is>
       </c>
     </row>
@@ -719,22 +719,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>294</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.10 [0.91, 1.32]</t>
+          <t>1.06 [0.87, 1.29]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.57</t>
         </is>
       </c>
     </row>
@@ -746,22 +746,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24 [0.98, 1.56]</t>
+          <t>1.07 [0.84, 1.37]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.56</t>
         </is>
       </c>
     </row>
@@ -773,22 +773,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>272</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.96 [0.81, 1.13]</t>
+          <t>0.93 [0.78, 1.10]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.39</t>
         </is>
       </c>
     </row>
@@ -800,22 +800,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>268</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>77</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.93 [0.77, 1.14]</t>
+          <t>0.95 [0.76, 1.19]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.67</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.88 [1.63, 2.16]</t>
+          <t>1.88 [1.64, 2.15]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.29 [2.54, 4.35]</t>
+          <t>3.29 [2.54, 4.34]</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.57 [1.34, 1.84]</t>
+          <t>1.57 [1.34, 1.81]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.27 [1.83, 2.91]</t>
+          <t>2.27 [1.84, 2.84]</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2753,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.10 [0.93, 1.29]</t>
+          <t>1.11 [0.94, 1.30]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.35 [1.02, 1.88]</t>
+          <t>1.34 [1.02, 1.89]</t>
         </is>
       </c>
     </row>
